--- a/tame_output/ON/bt/strategyON_20240306.xlsx
+++ b/tame_output/ON/bt/strategyON_20240306.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-573.2%</t>
+          <t>-584.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-109.6%</t>
+          <t>-109.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-37.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>-84.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100.9%</t>
+          <t>101.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.1%</t>
+          <t>-44.7%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.406754967078532</v>
+        <v>3.406754967078534</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>0.5201841138885551</v>
+        <v>0.5258221424517131</v>
       </c>
       <c r="E1894" t="n">
-        <v>3.383337215597817</v>
+        <v>3.38559242702308</v>
       </c>
       <c r="F1894" t="n">
-        <v>1.390176077562696</v>
+        <v>1.395814106125854</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.009725640893761</v>
+        <v>4.013108458031655</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240306.xlsx
+++ b/tame_output/ON/bt/strategyON_20240306.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-584.6%</t>
+          <t>-589.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-109.0%</t>
+          <t>-108.7%</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-84.4%</t>
+          <t>-84.2%</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-44.7%</t>
+          <t>-44.6%</t>
         </is>
       </c>
     </row>
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>0.5258221424517131</v>
+        <v>0.5283922243809037</v>
       </c>
       <c r="E1894" t="n">
-        <v>3.38559242702308</v>
+        <v>3.386620459794757</v>
       </c>
       <c r="F1894" t="n">
-        <v>1.395814106125854</v>
+        <v>1.398384188055045</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.013108458031655</v>
+        <v>4.014650507189169</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240306.xlsx
+++ b/tame_output/ON/bt/strategyON_20240306.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-589.7%</t>
+          <t>-138.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-108.7%</t>
+          <t>-131.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-46.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-84.2%</t>
+          <t>-106.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>101.0%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-44.6%</t>
+          <t>-58.0%</t>
         </is>
       </c>
     </row>
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>0.5283922243809037</v>
+        <v>0.3037317655783706</v>
       </c>
       <c r="E1894" t="n">
-        <v>3.386620459794757</v>
+        <v>3.296756276273744</v>
       </c>
       <c r="F1894" t="n">
-        <v>1.398384188055045</v>
+        <v>1.173723729252512</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.014650507189169</v>
+        <v>3.879854231907649</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240306.xlsx
+++ b/tame_output/ON/bt/strategyON_20240306.xlsx
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
